--- a/dietitian_forms/004_food_allergy_form--dietitian_forms.xlsx
+++ b/dietitian_forms/004_food_allergy_form--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'egg'}</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Egg'}</t>
+          <t>Egg</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poultry'}</t>
+          <t>poultry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poultry'}</t>
+          <t>Poultry</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'tree_nut'}</t>
+          <t>tree_nut</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Tree nut'}</t>
+          <t>Tree nut</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'wheat'}</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Wheat'}</t>
+          <t>Wheat</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'epi_pen'}</t>
+          <t>epi_pen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'epi_pen'}</t>
+          <t>epi pen</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other_medication_allergy'}</t>
+          <t>other_medication_allergy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other_medication_allergy'}</t>
+          <t>other medication allergy</t>
         </is>
       </c>
     </row>
